--- a/बजेट माग estimate/prahari chauki nangle windows.xlsx
+++ b/बजेट माग estimate/prahari chauki nangle windows.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D690E2DE-89FC-4769-ABFF-18FFD63E0592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Estimate (4)" sheetId="10" state="hidden" r:id="rId1"/>
@@ -40,10 +39,10 @@
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Estimate (4)'!$A$5:$K$66</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Police sector contribution'!$A$5:$K$66</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Police sector contribution (2)'!$A$1:$K$91</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Police sector contribution (2)'!$A$1:$K$106</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Police sector contribution (2)'!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -58,8 +57,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="G91" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+area of cone = pi() * r * sqrt(r^2+ht^2)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="82">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -269,17 +300,53 @@
   </si>
   <si>
     <t>-Kitchen</t>
+  </si>
+  <si>
+    <t>sfnf] kmnfd] kfO{ksf] 6«; agfO{ h8fg ug]{ sfd</t>
+  </si>
+  <si>
+    <t>Length (m)</t>
+  </si>
+  <si>
+    <t>Unit Weight (kg/m)</t>
+  </si>
+  <si>
+    <t>Weight  (kg)</t>
+  </si>
+  <si>
+    <t>).#^ lblv ).$ dL.dL.afSnf] sf]?u]6]8 /+lug ss{6 kftfsf] 5fgf 5fpg] sfd</t>
+  </si>
+  <si>
+    <t>-3" MS square pipe 1.6mm thick for vertical post</t>
+  </si>
+  <si>
+    <t>-for roofing</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>- 1.5" MS square pipe 1.6mm thick for inclined members</t>
+  </si>
+  <si>
+    <t>-1.5" MS hollow pipe 1.6mm thick for horizontal member</t>
+  </si>
+  <si>
+    <t>Provisional sum for other unforseen works</t>
+  </si>
+  <si>
+    <t>PS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,6 +514,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -523,25 +601,25 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -556,7 +634,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -594,7 +672,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -603,7 +681,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -640,14 +718,14 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -666,7 +744,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -681,11 +759,48 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -724,6 +839,24 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -743,69 +876,32 @@
     <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3" xr:uid="{C2B1C13C-EE6C-4219-85EC-18643C440D1C}"/>
+    <cellStyle name="Comma 2" xfId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{17066CD6-EF50-4F78-A82E-5F783A7CF4D2}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{A02DDCC0-68F7-40DD-9EC3-4BCC6842B6D9}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{74C92E6C-9A23-4F52-BEC1-66ED46887BD7}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="5"/>
+    <cellStyle name="Percent 2" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -821,7 +917,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -915,7 +1011,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -974,9 +1070,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1014,9 +1110,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1051,7 +1147,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1086,7 +1182,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1259,131 +1355,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+    </row>
+    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="s">
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="76" t="s">
+      <c r="H7" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="76"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="89"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="89"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -1418,7 +1514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A9" s="30">
         <v>1</v>
       </c>
@@ -1435,7 +1531,7 @@
       <c r="J9" s="20"/>
       <c r="K9" s="20"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="30"/>
       <c r="B10" s="31" t="s">
         <v>25</v>
@@ -1462,7 +1558,7 @@
       <c r="J10" s="20"/>
       <c r="K10" s="20"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="30"/>
       <c r="B11" s="31"/>
       <c r="C11" s="32">
@@ -1486,7 +1582,7 @@
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="30"/>
       <c r="B12" s="31" t="s">
         <v>26</v>
@@ -1513,7 +1609,7 @@
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="9" t="s">
         <v>18</v>
@@ -1538,7 +1634,7 @@
       </c>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="30"/>
       <c r="B14" s="34" t="s">
         <v>27</v>
@@ -1556,7 +1652,7 @@
       </c>
       <c r="K14" s="20"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="30"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -1569,7 +1665,7 @@
       <c r="J15" s="20"/>
       <c r="K15" s="20"/>
     </row>
-    <row r="16" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A16" s="30">
         <v>2</v>
       </c>
@@ -1586,7 +1682,7 @@
       <c r="J16" s="20"/>
       <c r="K16" s="20"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="30"/>
       <c r="B17" s="31" t="str">
         <f>B12</f>
@@ -1615,7 +1711,7 @@
       <c r="J17" s="20"/>
       <c r="K17" s="20"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="9" t="s">
         <v>18</v>
@@ -1640,7 +1736,7 @@
       </c>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="30"/>
       <c r="B19" s="34" t="s">
         <v>27</v>
@@ -1658,7 +1754,7 @@
       </c>
       <c r="K19" s="20"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="30"/>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -1671,7 +1767,7 @@
       <c r="J20" s="20"/>
       <c r="K20" s="20"/>
     </row>
-    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A21" s="30">
         <v>3</v>
       </c>
@@ -1688,7 +1784,7 @@
       <c r="J21" s="20"/>
       <c r="K21" s="20"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="30"/>
       <c r="B22" s="31" t="str">
         <f>B10</f>
@@ -1714,7 +1810,7 @@
       <c r="J22" s="20"/>
       <c r="K22" s="20"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="30"/>
       <c r="B23" s="31"/>
       <c r="C23" s="32">
@@ -1739,7 +1835,7 @@
       <c r="J23" s="20"/>
       <c r="K23" s="20"/>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="9" t="s">
         <v>18</v>
@@ -1764,7 +1860,7 @@
       </c>
       <c r="K24" s="12"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="30"/>
       <c r="B25" s="34" t="s">
         <v>27</v>
@@ -1782,7 +1878,7 @@
       </c>
       <c r="K25" s="20"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="30"/>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -1795,7 +1891,7 @@
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
     </row>
-    <row r="27" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="69" x14ac:dyDescent="0.3">
       <c r="A27" s="30">
         <v>4</v>
       </c>
@@ -1812,7 +1908,7 @@
       <c r="J27" s="20"/>
       <c r="K27" s="20"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="30"/>
       <c r="B28" s="31" t="str">
         <f>B10</f>
@@ -1840,7 +1936,7 @@
       <c r="J28" s="20"/>
       <c r="K28" s="20"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="30"/>
       <c r="B29" s="31"/>
       <c r="C29" s="20">
@@ -1865,7 +1961,7 @@
       <c r="J29" s="20"/>
       <c r="K29" s="20"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="30"/>
       <c r="B30" s="31"/>
       <c r="C30" s="20">
@@ -1892,7 +1988,7 @@
       <c r="J30" s="20"/>
       <c r="K30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="30"/>
       <c r="B31" s="31"/>
       <c r="C31" s="20">
@@ -1917,7 +2013,7 @@
       <c r="J31" s="20"/>
       <c r="K31" s="20"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="30"/>
       <c r="B32" s="31" t="str">
         <f>B12</f>
@@ -1946,7 +2042,7 @@
       <c r="J32" s="20"/>
       <c r="K32" s="20"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="30"/>
       <c r="B33" s="31"/>
       <c r="C33" s="32">
@@ -1971,7 +2067,7 @@
       <c r="J33" s="20"/>
       <c r="K33" s="20"/>
     </row>
-    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="9" t="s">
         <v>18</v>
@@ -1996,7 +2092,7 @@
       </c>
       <c r="K34" s="12"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="30"/>
       <c r="B35" s="34" t="s">
         <v>27</v>
@@ -2014,7 +2110,7 @@
       </c>
       <c r="K35" s="20"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="30"/>
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
@@ -2027,7 +2123,7 @@
       <c r="J36" s="20"/>
       <c r="K36" s="20"/>
     </row>
-    <row r="37" spans="1:11" ht="32.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="33" x14ac:dyDescent="0.3">
       <c r="A37" s="30">
         <v>5</v>
       </c>
@@ -2044,7 +2140,7 @@
       <c r="J37" s="20"/>
       <c r="K37" s="20"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="30"/>
       <c r="B38" s="31" t="str">
         <f>B10</f>
@@ -2073,7 +2169,7 @@
       <c r="J38" s="20"/>
       <c r="K38" s="20"/>
     </row>
-    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
@@ -2098,7 +2194,7 @@
       </c>
       <c r="K39" s="12"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="30"/>
       <c r="B40" s="34" t="s">
         <v>27</v>
@@ -2116,7 +2212,7 @@
       </c>
       <c r="K40" s="20"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="30"/>
       <c r="B41" s="34"/>
       <c r="C41" s="20"/>
@@ -2129,7 +2225,7 @@
       <c r="J41" s="15"/>
       <c r="K41" s="20"/>
     </row>
-    <row r="42" spans="1:11" s="16" customFormat="1" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" s="16" customFormat="1" ht="32.4" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>6</v>
       </c>
@@ -2146,7 +2242,7 @@
       <c r="J42" s="40"/>
       <c r="K42" s="12"/>
     </row>
-    <row r="43" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="41" t="str">
         <f>B28</f>
@@ -2172,7 +2268,7 @@
       <c r="J43" s="40"/>
       <c r="K43" s="12"/>
     </row>
-    <row r="44" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="41" t="s">
         <v>38</v>
@@ -2197,7 +2293,7 @@
       </c>
       <c r="K44" s="12"/>
     </row>
-    <row r="45" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="41" t="s">
         <v>40</v>
@@ -2215,7 +2311,7 @@
       </c>
       <c r="K45" s="12"/>
     </row>
-    <row r="46" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="39"/>
       <c r="C46" s="10"/>
@@ -2228,7 +2324,7 @@
       <c r="J46" s="40"/>
       <c r="K46" s="12"/>
     </row>
-    <row r="47" spans="1:11" s="16" customFormat="1" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" s="16" customFormat="1" ht="32.4" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>7</v>
       </c>
@@ -2245,7 +2341,7 @@
       <c r="J47" s="40"/>
       <c r="K47" s="12"/>
     </row>
-    <row r="48" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="41" t="str">
         <f>B43</f>
@@ -2271,7 +2367,7 @@
       <c r="J48" s="40"/>
       <c r="K48" s="12"/>
     </row>
-    <row r="49" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="41" t="s">
         <v>38</v>
@@ -2296,7 +2392,7 @@
       </c>
       <c r="K49" s="12"/>
     </row>
-    <row r="50" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="41" t="s">
         <v>40</v>
@@ -2314,7 +2410,7 @@
       </c>
       <c r="K50" s="12"/>
     </row>
-    <row r="51" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="39"/>
       <c r="C51" s="10"/>
@@ -2327,7 +2423,7 @@
       <c r="J51" s="40"/>
       <c r="K51" s="12"/>
     </row>
-    <row r="52" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A52" s="30">
         <v>8</v>
       </c>
@@ -2344,7 +2440,7 @@
       <c r="J52" s="20"/>
       <c r="K52" s="20"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="30"/>
       <c r="B53" s="31" t="str">
         <f>B12</f>
@@ -2373,7 +2469,7 @@
       <c r="J53" s="20"/>
       <c r="K53" s="20"/>
     </row>
-    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="9" t="s">
         <v>18</v>
@@ -2398,7 +2494,7 @@
       </c>
       <c r="K54" s="12"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="30"/>
       <c r="B55" s="34" t="s">
         <v>27</v>
@@ -2416,7 +2512,7 @@
       </c>
       <c r="K55" s="20"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="30"/>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
@@ -2429,7 +2525,7 @@
       <c r="J56" s="20"/>
       <c r="K56" s="20"/>
     </row>
-    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>9</v>
       </c>
@@ -2458,7 +2554,7 @@
       </c>
       <c r="K57" s="12"/>
     </row>
-    <row r="58" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
       <c r="B58" s="21"/>
       <c r="C58" s="10"/>
@@ -2471,7 +2567,7 @@
       <c r="J58" s="15"/>
       <c r="K58" s="12"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="19"/>
       <c r="B59" s="28" t="s">
         <v>23</v>
@@ -2489,16 +2585,16 @@
       </c>
       <c r="K59" s="17"/>
     </row>
-    <row r="61" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23"/>
       <c r="B61" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="65">
+      <c r="C61" s="78">
         <f>J59</f>
         <v>1071666.46048649</v>
       </c>
-      <c r="D61" s="66"/>
+      <c r="D61" s="79"/>
       <c r="E61" s="38">
         <v>100</v>
       </c>
@@ -2509,66 +2605,66 @@
       <c r="J61" s="26"/>
       <c r="K61" s="27"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B62" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C62" s="71">
+      <c r="C62" s="84">
         <v>950000</v>
       </c>
-      <c r="D62" s="72"/>
+      <c r="D62" s="85"/>
       <c r="E62" s="38"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B63" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C63" s="71">
+      <c r="C63" s="84">
         <f>C62-C65-C66</f>
         <v>902500</v>
       </c>
-      <c r="D63" s="72"/>
+      <c r="D63" s="85"/>
       <c r="E63" s="38">
         <f>C63/C61*100</f>
         <v>84.214635175790065</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B64" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="77">
+      <c r="C64" s="90">
         <f>C61-C63</f>
         <v>169166.46048649005</v>
       </c>
-      <c r="D64" s="77"/>
+      <c r="D64" s="90"/>
       <c r="E64" s="38">
         <f>100-E63</f>
         <v>15.785364824209935</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="C65" s="65">
+      <c r="C65" s="78">
         <f>C62*0.03</f>
         <v>28500</v>
       </c>
-      <c r="D65" s="66"/>
+      <c r="D65" s="79"/>
       <c r="E65" s="38">
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C66" s="65">
+      <c r="C66" s="78">
         <f>C62*0.02</f>
         <v>19000</v>
       </c>
-      <c r="D66" s="66"/>
+      <c r="D66" s="79"/>
       <c r="E66" s="38">
         <v>2</v>
       </c>
@@ -2597,131 +2693,131 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+    </row>
+    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="s">
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="76" t="s">
+      <c r="H7" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="76"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="89"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="89"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -2756,7 +2852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A9" s="30">
         <v>1</v>
       </c>
@@ -2773,7 +2869,7 @@
       <c r="J9" s="20"/>
       <c r="K9" s="20"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="30"/>
       <c r="B10" s="31" t="s">
         <v>25</v>
@@ -2800,7 +2896,7 @@
       <c r="J10" s="20"/>
       <c r="K10" s="20"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="30"/>
       <c r="B11" s="31"/>
       <c r="C11" s="32">
@@ -2824,7 +2920,7 @@
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="30"/>
       <c r="B12" s="31" t="s">
         <v>26</v>
@@ -2851,7 +2947,7 @@
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="9" t="s">
         <v>18</v>
@@ -2876,7 +2972,7 @@
       </c>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="30"/>
       <c r="B14" s="34" t="s">
         <v>27</v>
@@ -2894,7 +2990,7 @@
       </c>
       <c r="K14" s="20"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="30"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -2907,7 +3003,7 @@
       <c r="J15" s="20"/>
       <c r="K15" s="20"/>
     </row>
-    <row r="16" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A16" s="30">
         <v>2</v>
       </c>
@@ -2924,7 +3020,7 @@
       <c r="J16" s="20"/>
       <c r="K16" s="20"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="30"/>
       <c r="B17" s="31" t="str">
         <f>B12</f>
@@ -2953,7 +3049,7 @@
       <c r="J17" s="20"/>
       <c r="K17" s="20"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="9" t="s">
         <v>18</v>
@@ -2978,7 +3074,7 @@
       </c>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="30"/>
       <c r="B19" s="34" t="s">
         <v>27</v>
@@ -2996,7 +3092,7 @@
       </c>
       <c r="K19" s="20"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="30"/>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -3009,7 +3105,7 @@
       <c r="J20" s="20"/>
       <c r="K20" s="20"/>
     </row>
-    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A21" s="30">
         <v>3</v>
       </c>
@@ -3026,7 +3122,7 @@
       <c r="J21" s="20"/>
       <c r="K21" s="20"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="30"/>
       <c r="B22" s="31" t="str">
         <f>B10</f>
@@ -3052,7 +3148,7 @@
       <c r="J22" s="20"/>
       <c r="K22" s="20"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="30"/>
       <c r="B23" s="31"/>
       <c r="C23" s="32">
@@ -3077,7 +3173,7 @@
       <c r="J23" s="20"/>
       <c r="K23" s="20"/>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="9" t="s">
         <v>18</v>
@@ -3102,7 +3198,7 @@
       </c>
       <c r="K24" s="12"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="30"/>
       <c r="B25" s="34" t="s">
         <v>27</v>
@@ -3120,7 +3216,7 @@
       </c>
       <c r="K25" s="20"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="30"/>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -3133,7 +3229,7 @@
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
     </row>
-    <row r="27" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="69" x14ac:dyDescent="0.3">
       <c r="A27" s="30">
         <v>4</v>
       </c>
@@ -3150,7 +3246,7 @@
       <c r="J27" s="20"/>
       <c r="K27" s="20"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="30"/>
       <c r="B28" s="31" t="str">
         <f>B10</f>
@@ -3178,7 +3274,7 @@
       <c r="J28" s="20"/>
       <c r="K28" s="20"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="30"/>
       <c r="B29" s="31"/>
       <c r="C29" s="20">
@@ -3203,7 +3299,7 @@
       <c r="J29" s="20"/>
       <c r="K29" s="20"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="30"/>
       <c r="B30" s="31"/>
       <c r="C30" s="20">
@@ -3230,7 +3326,7 @@
       <c r="J30" s="20"/>
       <c r="K30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="30"/>
       <c r="B31" s="31"/>
       <c r="C31" s="20">
@@ -3255,7 +3351,7 @@
       <c r="J31" s="20"/>
       <c r="K31" s="20"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="30"/>
       <c r="B32" s="31" t="str">
         <f>B12</f>
@@ -3284,7 +3380,7 @@
       <c r="J32" s="20"/>
       <c r="K32" s="20"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="30"/>
       <c r="B33" s="31"/>
       <c r="C33" s="32">
@@ -3309,7 +3405,7 @@
       <c r="J33" s="20"/>
       <c r="K33" s="20"/>
     </row>
-    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="9" t="s">
         <v>18</v>
@@ -3334,7 +3430,7 @@
       </c>
       <c r="K34" s="12"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="30"/>
       <c r="B35" s="34" t="s">
         <v>27</v>
@@ -3352,7 +3448,7 @@
       </c>
       <c r="K35" s="20"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="30"/>
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
@@ -3365,7 +3461,7 @@
       <c r="J36" s="20"/>
       <c r="K36" s="20"/>
     </row>
-    <row r="37" spans="1:11" ht="32.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="33" x14ac:dyDescent="0.3">
       <c r="A37" s="30">
         <v>5</v>
       </c>
@@ -3382,7 +3478,7 @@
       <c r="J37" s="20"/>
       <c r="K37" s="20"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="30"/>
       <c r="B38" s="31" t="str">
         <f>B10</f>
@@ -3411,7 +3507,7 @@
       <c r="J38" s="20"/>
       <c r="K38" s="20"/>
     </row>
-    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
@@ -3436,7 +3532,7 @@
       </c>
       <c r="K39" s="12"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="30"/>
       <c r="B40" s="34" t="s">
         <v>27</v>
@@ -3454,7 +3550,7 @@
       </c>
       <c r="K40" s="20"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="30"/>
       <c r="B41" s="34"/>
       <c r="C41" s="20"/>
@@ -3467,7 +3563,7 @@
       <c r="J41" s="15"/>
       <c r="K41" s="20"/>
     </row>
-    <row r="42" spans="1:11" s="16" customFormat="1" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" s="16" customFormat="1" ht="32.4" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>6</v>
       </c>
@@ -3484,7 +3580,7 @@
       <c r="J42" s="40"/>
       <c r="K42" s="12"/>
     </row>
-    <row r="43" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="41" t="str">
         <f>B28</f>
@@ -3510,7 +3606,7 @@
       <c r="J43" s="40"/>
       <c r="K43" s="12"/>
     </row>
-    <row r="44" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="41" t="s">
         <v>38</v>
@@ -3535,7 +3631,7 @@
       </c>
       <c r="K44" s="12"/>
     </row>
-    <row r="45" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="41" t="s">
         <v>40</v>
@@ -3553,7 +3649,7 @@
       </c>
       <c r="K45" s="12"/>
     </row>
-    <row r="46" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="39"/>
       <c r="C46" s="10"/>
@@ -3566,7 +3662,7 @@
       <c r="J46" s="40"/>
       <c r="K46" s="12"/>
     </row>
-    <row r="47" spans="1:11" s="16" customFormat="1" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" s="16" customFormat="1" ht="32.4" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>7</v>
       </c>
@@ -3583,7 +3679,7 @@
       <c r="J47" s="40"/>
       <c r="K47" s="12"/>
     </row>
-    <row r="48" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="41" t="str">
         <f>B43</f>
@@ -3609,7 +3705,7 @@
       <c r="J48" s="40"/>
       <c r="K48" s="12"/>
     </row>
-    <row r="49" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="41" t="s">
         <v>38</v>
@@ -3634,7 +3730,7 @@
       </c>
       <c r="K49" s="12"/>
     </row>
-    <row r="50" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="41" t="s">
         <v>40</v>
@@ -3652,7 +3748,7 @@
       </c>
       <c r="K50" s="12"/>
     </row>
-    <row r="51" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="39"/>
       <c r="C51" s="10"/>
@@ -3665,7 +3761,7 @@
       <c r="J51" s="40"/>
       <c r="K51" s="12"/>
     </row>
-    <row r="52" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A52" s="30">
         <v>8</v>
       </c>
@@ -3682,7 +3778,7 @@
       <c r="J52" s="20"/>
       <c r="K52" s="20"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="30"/>
       <c r="B53" s="31" t="str">
         <f>B12</f>
@@ -3711,7 +3807,7 @@
       <c r="J53" s="20"/>
       <c r="K53" s="20"/>
     </row>
-    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="9" t="s">
         <v>18</v>
@@ -3736,7 +3832,7 @@
       </c>
       <c r="K54" s="12"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="30"/>
       <c r="B55" s="34" t="s">
         <v>27</v>
@@ -3754,7 +3850,7 @@
       </c>
       <c r="K55" s="20"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="30"/>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
@@ -3767,7 +3863,7 @@
       <c r="J56" s="20"/>
       <c r="K56" s="20"/>
     </row>
-    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>9</v>
       </c>
@@ -3796,7 +3892,7 @@
       </c>
       <c r="K57" s="12"/>
     </row>
-    <row r="58" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
       <c r="B58" s="21"/>
       <c r="C58" s="10"/>
@@ -3809,7 +3905,7 @@
       <c r="J58" s="15"/>
       <c r="K58" s="12"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="19"/>
       <c r="B59" s="28" t="s">
         <v>23</v>
@@ -3827,16 +3923,16 @@
       </c>
       <c r="K59" s="17"/>
     </row>
-    <row r="61" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23"/>
       <c r="B61" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="65">
+      <c r="C61" s="78">
         <f>J59</f>
         <v>797572.48017999006</v>
       </c>
-      <c r="D61" s="66"/>
+      <c r="D61" s="79"/>
       <c r="E61" s="38">
         <v>100</v>
       </c>
@@ -3847,72 +3943,79 @@
       <c r="J61" s="26"/>
       <c r="K61" s="27"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B62" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C62" s="71">
+      <c r="C62" s="84">
         <v>500000</v>
       </c>
-      <c r="D62" s="72"/>
+      <c r="D62" s="85"/>
       <c r="E62" s="38"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B63" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C63" s="71">
+      <c r="C63" s="84">
         <f>C62-C65-C66</f>
         <v>475000</v>
       </c>
-      <c r="D63" s="72"/>
+      <c r="D63" s="85"/>
       <c r="E63" s="38">
         <f>C63/C61*100</f>
         <v>59.555715850778299</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B64" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="C64" s="77">
+      <c r="C64" s="90">
         <f>C61-C63</f>
         <v>322572.48017999006</v>
       </c>
-      <c r="D64" s="77"/>
+      <c r="D64" s="90"/>
       <c r="E64" s="38">
         <f>100-E63</f>
         <v>40.444284149221701</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="C65" s="65">
+      <c r="C65" s="78">
         <f>C62*0.03</f>
         <v>15000</v>
       </c>
-      <c r="D65" s="66"/>
+      <c r="D65" s="79"/>
       <c r="E65" s="38">
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C66" s="65">
+      <c r="C66" s="78">
         <f>C62*0.02</f>
         <v>10000</v>
       </c>
-      <c r="D66" s="66"/>
+      <c r="D66" s="79"/>
       <c r="E66" s="38">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C65:D65"/>
     <mergeCell ref="C66:D66"/>
     <mergeCell ref="A7:F7"/>
@@ -3921,13 +4024,6 @@
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="C64:D64"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -3935,133 +4031,133 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S91"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S106"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="52" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" style="52" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" style="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="52" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="52" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="52" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="52"/>
+    <col min="1" max="1" width="4.6640625" style="52" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" style="52" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" style="52" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" style="52" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="52" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="52"/>
     <col min="8" max="8" width="5" style="52" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="52" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="52"/>
+    <col min="9" max="9" width="9.5546875" style="52" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" style="52" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-    </row>
-    <row r="2" spans="1:13" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="89" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+    </row>
+    <row r="2" spans="1:13" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="94" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="89" t="s">
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-    </row>
-    <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="90" t="s">
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+    </row>
+    <row r="5" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="90"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="85" t="s">
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+    </row>
+    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
       <c r="G6" s="43"/>
-      <c r="H6" s="86" t="s">
+      <c r="H6" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="80" t="s">
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+    </row>
+    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
       <c r="G7" s="44"/>
-      <c r="H7" s="81" t="s">
+      <c r="H7" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="45" t="s">
         <v>6</v>
       </c>
@@ -4096,11 +4192,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="99">
-        <v>1</v>
-      </c>
-      <c r="B9" s="100" t="s">
+    <row r="9" spans="1:13" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A9" s="73">
+        <v>1</v>
+      </c>
+      <c r="B9" s="74" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="32"/>
@@ -4112,11 +4208,11 @@
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
       <c r="K9" s="50"/>
-      <c r="M9" s="92"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="99"/>
-      <c r="B10" s="103" t="s">
+      <c r="M9" s="66"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="73"/>
+      <c r="B10" s="77" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="32"/>
@@ -4129,8 +4225,8 @@
       <c r="J10" s="32"/>
       <c r="K10" s="50"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="99"/>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="73"/>
       <c r="B11" s="31" t="s">
         <v>47</v>
       </c>
@@ -4153,8 +4249,8 @@
       <c r="J11" s="32"/>
       <c r="K11" s="50"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="99"/>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="73"/>
       <c r="B12" s="31"/>
       <c r="C12" s="32">
         <v>1</v>
@@ -4175,8 +4271,8 @@
       <c r="J12" s="32"/>
       <c r="K12" s="50"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="99"/>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="73"/>
       <c r="B13" s="31" t="s">
         <v>54</v>
       </c>
@@ -4199,8 +4295,8 @@
       <c r="J13" s="32"/>
       <c r="K13" s="50"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="99"/>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="73"/>
       <c r="B14" s="31"/>
       <c r="C14" s="32">
         <v>1</v>
@@ -4221,8 +4317,8 @@
       <c r="J14" s="32"/>
       <c r="K14" s="50"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="99"/>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="73"/>
       <c r="B15" s="31"/>
       <c r="C15" s="32">
         <v>1</v>
@@ -4243,8 +4339,8 @@
       <c r="J15" s="32"/>
       <c r="K15" s="50"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="99"/>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="73"/>
       <c r="B16" s="31" t="s">
         <v>57</v>
       </c>
@@ -4267,8 +4363,8 @@
       <c r="J16" s="32"/>
       <c r="K16" s="50"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="99"/>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="73"/>
       <c r="B17" s="31"/>
       <c r="C17" s="32">
         <f>2</f>
@@ -4291,8 +4387,8 @@
       <c r="J17" s="32"/>
       <c r="K17" s="50"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="99"/>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="73"/>
       <c r="B18" s="31" t="s">
         <v>61</v>
       </c>
@@ -4315,8 +4411,8 @@
       <c r="J18" s="32"/>
       <c r="K18" s="50"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="99"/>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="73"/>
       <c r="B19" s="31"/>
       <c r="C19" s="32">
         <v>1</v>
@@ -4337,7 +4433,7 @@
       <c r="J19" s="32"/>
       <c r="K19" s="50"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="49"/>
       <c r="B20" s="31" t="s">
         <v>62</v>
@@ -4361,7 +4457,7 @@
       <c r="J20" s="32"/>
       <c r="K20" s="50"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="49"/>
       <c r="B21" s="31"/>
       <c r="C21" s="32">
@@ -4383,9 +4479,9 @@
       <c r="J21" s="32"/>
       <c r="K21" s="50"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="99"/>
-      <c r="B22" s="103" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="73"/>
+      <c r="B22" s="77" t="s">
         <v>64</v>
       </c>
       <c r="C22" s="32"/>
@@ -4398,8 +4494,8 @@
       <c r="J22" s="32"/>
       <c r="K22" s="50"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="99"/>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="73"/>
       <c r="B23" s="31" t="s">
         <v>61</v>
       </c>
@@ -4422,8 +4518,8 @@
       <c r="J23" s="32"/>
       <c r="K23" s="50"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="99"/>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="73"/>
       <c r="B24" s="31"/>
       <c r="C24" s="32">
         <v>1</v>
@@ -4444,8 +4540,8 @@
       <c r="J24" s="32"/>
       <c r="K24" s="50"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="99"/>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="73"/>
       <c r="B25" s="31"/>
       <c r="C25" s="32">
         <v>1</v>
@@ -4466,8 +4562,8 @@
       <c r="J25" s="32"/>
       <c r="K25" s="50"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="99"/>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="73"/>
       <c r="B26" s="31" t="s">
         <v>66</v>
       </c>
@@ -4490,8 +4586,8 @@
       <c r="J26" s="32"/>
       <c r="K26" s="50"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="99"/>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="73"/>
       <c r="B27" s="31" t="s">
         <v>61</v>
       </c>
@@ -4505,9 +4601,9 @@
       <c r="J27" s="32"/>
       <c r="K27" s="50"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="99"/>
-      <c r="B28" s="103" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="73"/>
+      <c r="B28" s="77" t="s">
         <v>68</v>
       </c>
       <c r="C28" s="32"/>
@@ -4520,8 +4616,8 @@
       <c r="J28" s="32"/>
       <c r="K28" s="50"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="99"/>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="73"/>
       <c r="B29" s="31" t="s">
         <v>61</v>
       </c>
@@ -4544,8 +4640,8 @@
       <c r="J29" s="32"/>
       <c r="K29" s="50"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="99"/>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="73"/>
       <c r="B30" s="31"/>
       <c r="C30" s="32">
         <v>1</v>
@@ -4566,33 +4662,33 @@
       <c r="J30" s="32"/>
       <c r="K30" s="50"/>
     </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="101"/>
-      <c r="B31" s="95" t="s">
+    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="75"/>
+      <c r="B31" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="96"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="94"/>
-      <c r="F31" s="94"/>
-      <c r="G31" s="93">
+      <c r="C31" s="70"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="67">
         <f>SUM(G11:G30)</f>
         <v>34.900770070100577</v>
       </c>
-      <c r="H31" s="97" t="s">
+      <c r="H31" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="I31" s="93">
+      <c r="I31" s="67">
         <v>6997</v>
       </c>
-      <c r="J31" s="98">
+      <c r="J31" s="72">
         <f>G31*I31</f>
         <v>244200.68818049374</v>
       </c>
       <c r="K31" s="12"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="99"/>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="73"/>
       <c r="B32" s="31" t="s">
         <v>27</v>
       </c>
@@ -4603,14 +4699,14 @@
       <c r="G32" s="32"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
-      <c r="J32" s="98">
+      <c r="J32" s="72">
         <f>0.13*J31</f>
         <v>31746.089463464188</v>
       </c>
       <c r="K32" s="50"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="99"/>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="73"/>
       <c r="B33" s="32"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
@@ -4622,26 +4718,26 @@
       <c r="J33" s="32"/>
       <c r="K33" s="50"/>
     </row>
-    <row r="34" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="99">
+    <row r="34" spans="1:11" s="53" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="73">
         <v>2</v>
       </c>
-      <c r="B34" s="100" t="s">
+      <c r="B34" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="50"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="99"/>
-      <c r="B35" s="103" t="s">
+      <c r="C34" s="107"/>
+      <c r="D34" s="107"/>
+      <c r="E34" s="107"/>
+      <c r="F34" s="107"/>
+      <c r="G34" s="107"/>
+      <c r="H34" s="107"/>
+      <c r="I34" s="107"/>
+      <c r="J34" s="107"/>
+      <c r="K34" s="60"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="73"/>
+      <c r="B35" s="77" t="s">
         <v>59</v>
       </c>
       <c r="C35" s="32"/>
@@ -4654,8 +4750,8 @@
       <c r="J35" s="32"/>
       <c r="K35" s="50"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="99"/>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="73"/>
       <c r="B36" s="31" t="s">
         <v>50</v>
       </c>
@@ -4679,8 +4775,8 @@
       <c r="J36" s="32"/>
       <c r="K36" s="50"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="99"/>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="73"/>
       <c r="B37" s="31" t="s">
         <v>51</v>
       </c>
@@ -4703,8 +4799,8 @@
       <c r="J37" s="32"/>
       <c r="K37" s="50"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="99"/>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="73"/>
       <c r="B38" s="31" t="s">
         <v>54</v>
       </c>
@@ -4727,8 +4823,8 @@
       <c r="J38" s="32"/>
       <c r="K38" s="50"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="99"/>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="73"/>
       <c r="B39" s="31" t="s">
         <v>55</v>
       </c>
@@ -4751,8 +4847,8 @@
       <c r="J39" s="32"/>
       <c r="K39" s="50"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="99"/>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="73"/>
       <c r="B40" s="31" t="s">
         <v>56</v>
       </c>
@@ -4775,8 +4871,8 @@
       <c r="J40" s="32"/>
       <c r="K40" s="50"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="99"/>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="73"/>
       <c r="B41" s="31" t="s">
         <v>60</v>
       </c>
@@ -4799,8 +4895,8 @@
       <c r="J41" s="32"/>
       <c r="K41" s="50"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="99"/>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="73"/>
       <c r="B42" s="31" t="s">
         <v>61</v>
       </c>
@@ -4823,8 +4919,8 @@
       <c r="J42" s="32"/>
       <c r="K42" s="50"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="99"/>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="73"/>
       <c r="B43" s="31"/>
       <c r="C43" s="32">
         <v>1</v>
@@ -4845,9 +4941,9 @@
       <c r="J43" s="32"/>
       <c r="K43" s="50"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="99"/>
-      <c r="B44" s="103" t="s">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="73"/>
+      <c r="B44" s="77" t="s">
         <v>64</v>
       </c>
       <c r="C44" s="32"/>
@@ -4860,8 +4956,8 @@
       <c r="J44" s="32"/>
       <c r="K44" s="50"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="99"/>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="73"/>
       <c r="B45" s="31" t="s">
         <v>61</v>
       </c>
@@ -4884,8 +4980,8 @@
       <c r="J45" s="32"/>
       <c r="K45" s="50"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="99"/>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="73"/>
       <c r="B46" s="31" t="s">
         <v>65</v>
       </c>
@@ -4908,8 +5004,8 @@
       <c r="J46" s="32"/>
       <c r="K46" s="50"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="99"/>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="73"/>
       <c r="B47" s="31" t="s">
         <v>66</v>
       </c>
@@ -4932,8 +5028,8 @@
       <c r="J47" s="32"/>
       <c r="K47" s="50"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="99"/>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="73"/>
       <c r="B48" s="31" t="s">
         <v>67</v>
       </c>
@@ -4956,9 +5052,9 @@
       <c r="J48" s="32"/>
       <c r="K48" s="50"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="99"/>
-      <c r="B49" s="103" t="s">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="73"/>
+      <c r="B49" s="77" t="s">
         <v>68</v>
       </c>
       <c r="C49" s="32"/>
@@ -4971,8 +5067,8 @@
       <c r="J49" s="32"/>
       <c r="K49" s="50"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="99"/>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="73"/>
       <c r="B50" s="31" t="s">
         <v>61</v>
       </c>
@@ -4995,8 +5091,8 @@
       <c r="J50" s="32"/>
       <c r="K50" s="50"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="99"/>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="73"/>
       <c r="B51" s="31"/>
       <c r="C51" s="32">
         <v>2</v>
@@ -5017,33 +5113,33 @@
       <c r="J51" s="32"/>
       <c r="K51" s="50"/>
     </row>
-    <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="101"/>
-      <c r="B52" s="95" t="s">
+    <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="75"/>
+      <c r="B52" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C52" s="96"/>
-      <c r="D52" s="91"/>
-      <c r="E52" s="94"/>
-      <c r="F52" s="94"/>
-      <c r="G52" s="93">
+      <c r="C52" s="70"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="67">
         <f>SUM(G36:G51)</f>
         <v>31.254199999999997</v>
       </c>
-      <c r="H52" s="97" t="s">
+      <c r="H52" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="I52" s="93">
+      <c r="I52" s="67">
         <v>8744</v>
       </c>
-      <c r="J52" s="98">
+      <c r="J52" s="72">
         <f>G52*I52</f>
         <v>273286.72479999997</v>
       </c>
       <c r="K52" s="12"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="99"/>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="73"/>
       <c r="B53" s="31" t="s">
         <v>27</v>
       </c>
@@ -5054,14 +5150,14 @@
       <c r="G53" s="32"/>
       <c r="H53" s="32"/>
       <c r="I53" s="32"/>
-      <c r="J53" s="98">
+      <c r="J53" s="72">
         <f>0.13*J52</f>
         <v>35527.274223999993</v>
       </c>
       <c r="K53" s="50"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="99"/>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="73"/>
       <c r="B54" s="32"/>
       <c r="C54" s="32"/>
       <c r="D54" s="32"/>
@@ -5073,11 +5169,11 @@
       <c r="J54" s="32"/>
       <c r="K54" s="50"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="99">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="73">
         <v>3</v>
       </c>
-      <c r="B55" s="102" t="s">
+      <c r="B55" s="76" t="s">
         <v>52</v>
       </c>
       <c r="C55" s="32"/>
@@ -5090,9 +5186,9 @@
       <c r="J55" s="32"/>
       <c r="K55" s="50"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="99"/>
-      <c r="B56" s="103" t="s">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="73"/>
+      <c r="B56" s="77" t="s">
         <v>59</v>
       </c>
       <c r="C56" s="32"/>
@@ -5105,8 +5201,8 @@
       <c r="J56" s="32"/>
       <c r="K56" s="50"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="99"/>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="73"/>
       <c r="B57" s="31" t="s">
         <v>53</v>
       </c>
@@ -5129,8 +5225,8 @@
       <c r="J57" s="32"/>
       <c r="K57" s="50"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="99"/>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="73"/>
       <c r="B58" s="31"/>
       <c r="C58" s="32">
         <v>1</v>
@@ -5151,7 +5247,7 @@
       <c r="J58" s="32"/>
       <c r="K58" s="50"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="49"/>
       <c r="B59" s="31"/>
       <c r="C59" s="32">
@@ -5173,7 +5269,7 @@
       <c r="J59" s="32"/>
       <c r="K59" s="50"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="49"/>
       <c r="B60" s="31"/>
       <c r="C60" s="32">
@@ -5195,7 +5291,7 @@
       <c r="J60" s="32"/>
       <c r="K60" s="50"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="49"/>
       <c r="B61" s="31" t="s">
         <v>54</v>
@@ -5219,7 +5315,7 @@
       <c r="J61" s="32"/>
       <c r="K61" s="50"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="49"/>
       <c r="B62" s="31"/>
       <c r="C62" s="32">
@@ -5241,7 +5337,7 @@
       <c r="J62" s="32"/>
       <c r="K62" s="50"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="49"/>
       <c r="B63" s="31" t="s">
         <v>60</v>
@@ -5265,9 +5361,9 @@
       <c r="J63" s="32"/>
       <c r="K63" s="50"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="99"/>
-      <c r="B64" s="103" t="s">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="73"/>
+      <c r="B64" s="77" t="s">
         <v>64</v>
       </c>
       <c r="C64" s="32"/>
@@ -5280,8 +5376,8 @@
       <c r="J64" s="32"/>
       <c r="K64" s="50"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="99"/>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="73"/>
       <c r="B65" s="31" t="s">
         <v>61</v>
       </c>
@@ -5304,8 +5400,8 @@
       <c r="J65" s="32"/>
       <c r="K65" s="50"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="99"/>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="73"/>
       <c r="B66" s="31"/>
       <c r="C66" s="32">
         <v>1</v>
@@ -5326,8 +5422,8 @@
       <c r="J66" s="32"/>
       <c r="K66" s="50"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="99"/>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="73"/>
       <c r="B67" s="31"/>
       <c r="C67" s="32">
         <v>4</v>
@@ -5348,9 +5444,9 @@
       <c r="J67" s="32"/>
       <c r="K67" s="50"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="99"/>
-      <c r="B68" s="103" t="s">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="73"/>
+      <c r="B68" s="77" t="s">
         <v>68</v>
       </c>
       <c r="C68" s="32"/>
@@ -5363,8 +5459,8 @@
       <c r="J68" s="32"/>
       <c r="K68" s="50"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="99"/>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="73"/>
       <c r="B69" s="31" t="s">
         <v>61</v>
       </c>
@@ -5387,8 +5483,8 @@
       <c r="J69" s="32"/>
       <c r="K69" s="50"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="99"/>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="73"/>
       <c r="B70" s="31"/>
       <c r="C70" s="32">
         <v>2</v>
@@ -5409,8 +5505,8 @@
       <c r="J70" s="32"/>
       <c r="K70" s="50"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="99"/>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="73"/>
       <c r="B71" s="31"/>
       <c r="C71" s="32">
         <v>1</v>
@@ -5431,7 +5527,7 @@
       <c r="J71" s="32"/>
       <c r="K71" s="50"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="49"/>
       <c r="B72" s="31" t="s">
         <v>69</v>
@@ -5455,32 +5551,32 @@
       <c r="J72" s="32"/>
       <c r="K72" s="50"/>
     </row>
-    <row r="73" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
-      <c r="B73" s="95" t="s">
+      <c r="B73" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C73" s="96"/>
-      <c r="D73" s="91"/>
-      <c r="E73" s="94"/>
-      <c r="F73" s="94"/>
-      <c r="G73" s="93">
+      <c r="C73" s="70"/>
+      <c r="D73" s="65"/>
+      <c r="E73" s="68"/>
+      <c r="F73" s="68"/>
+      <c r="G73" s="67">
         <f>SUM(G57:G72)</f>
         <v>27.544499999999999</v>
       </c>
-      <c r="H73" s="97" t="s">
+      <c r="H73" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="I73" s="93">
+      <c r="I73" s="67">
         <v>850.04</v>
       </c>
-      <c r="J73" s="98">
+      <c r="J73" s="72">
         <f>G73*I73</f>
         <v>23413.926779999998</v>
       </c>
       <c r="K73" s="12"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="49"/>
       <c r="B74" s="31" t="s">
         <v>27</v>
@@ -5492,13 +5588,13 @@
       <c r="G74" s="32"/>
       <c r="H74" s="32"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="98">
+      <c r="J74" s="72">
         <f>0.13*J73</f>
         <v>3043.8104813999998</v>
       </c>
       <c r="K74" s="50"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="49"/>
       <c r="B75" s="50"/>
       <c r="C75" s="50"/>
@@ -5511,11 +5607,11 @@
       <c r="J75" s="50"/>
       <c r="K75" s="50"/>
     </row>
-    <row r="76" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="99">
+    <row r="76" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="73">
         <v>4</v>
       </c>
-      <c r="B76" s="100" t="s">
+      <c r="B76" s="74" t="s">
         <v>63</v>
       </c>
       <c r="C76" s="32"/>
@@ -5528,9 +5624,9 @@
       <c r="J76" s="32"/>
       <c r="K76" s="50"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="99"/>
-      <c r="B77" s="103" t="s">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="73"/>
+      <c r="B77" s="77" t="s">
         <v>59</v>
       </c>
       <c r="C77" s="32"/>
@@ -5543,8 +5639,8 @@
       <c r="J77" s="32"/>
       <c r="K77" s="50"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="99"/>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="73"/>
       <c r="B78" s="31" t="s">
         <v>58</v>
       </c>
@@ -5567,32 +5663,32 @@
       <c r="J78" s="32"/>
       <c r="K78" s="50"/>
     </row>
-    <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>
-      <c r="B79" s="95" t="s">
+      <c r="B79" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C79" s="96"/>
-      <c r="D79" s="91"/>
-      <c r="E79" s="94"/>
-      <c r="F79" s="94"/>
-      <c r="G79" s="93">
+      <c r="C79" s="70"/>
+      <c r="D79" s="65"/>
+      <c r="E79" s="68"/>
+      <c r="F79" s="68"/>
+      <c r="G79" s="67">
         <f>SUM(G78:G78)</f>
         <v>5.2274999999999991</v>
       </c>
-      <c r="H79" s="97" t="s">
+      <c r="H79" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="I79" s="93">
+      <c r="I79" s="67">
         <v>9036</v>
       </c>
-      <c r="J79" s="98">
+      <c r="J79" s="72">
         <f>G79*I79</f>
         <v>47235.689999999995</v>
       </c>
       <c r="K79" s="12"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="49"/>
       <c r="B80" s="31" t="s">
         <v>27</v>
@@ -5604,13 +5700,13 @@
       <c r="G80" s="32"/>
       <c r="H80" s="32"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="98">
+      <c r="J80" s="72">
         <f>0.13*J79</f>
         <v>6140.6396999999997</v>
       </c>
       <c r="K80" s="50"/>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="49"/>
       <c r="B81" s="50"/>
       <c r="C81" s="50"/>
@@ -5623,168 +5719,522 @@
       <c r="J81" s="50"/>
       <c r="K81" s="50"/>
     </row>
-    <row r="82" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="8">
-        <v>9</v>
-      </c>
-      <c r="B82" s="7" t="s">
+    <row r="82" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A82" s="49">
+        <v>5</v>
+      </c>
+      <c r="B82" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C82" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="105" t="s">
+        <v>71</v>
+      </c>
+      <c r="E82" s="105" t="s">
+        <v>72</v>
+      </c>
+      <c r="F82" s="105" t="s">
+        <v>73</v>
+      </c>
+      <c r="G82" s="50"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="50"/>
+    </row>
+    <row r="83" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="73"/>
+      <c r="B83" s="108" t="s">
+        <v>75</v>
+      </c>
+      <c r="C83" s="32">
+        <v>7</v>
+      </c>
+      <c r="D83" s="33">
+        <f>(10+1.17)/3.281</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="E83" s="33">
+        <v>3.54</v>
+      </c>
+      <c r="F83" s="33">
+        <f>C83*D83*E83</f>
+        <v>84.362267601341046</v>
+      </c>
+      <c r="G83" s="33">
+        <f>F83</f>
+        <v>84.362267601341046</v>
+      </c>
+      <c r="H83" s="32"/>
+      <c r="I83" s="32"/>
+      <c r="J83" s="32"/>
+      <c r="K83" s="50"/>
+    </row>
+    <row r="84" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="73"/>
+      <c r="B84" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="C84" s="32">
+        <v>7</v>
+      </c>
+      <c r="D84" s="33">
+        <f>SQRT(D91^2+E91^2)</f>
+        <v>2.2188692134350858</v>
+      </c>
+      <c r="E84" s="33">
+        <v>1.83</v>
+      </c>
+      <c r="F84" s="33">
+        <f>C84*D84*E84</f>
+        <v>28.42371462410345</v>
+      </c>
+      <c r="G84" s="33">
+        <f>F84</f>
+        <v>28.42371462410345</v>
+      </c>
+      <c r="H84" s="32"/>
+      <c r="I84" s="32"/>
+      <c r="J84" s="32"/>
+      <c r="K84" s="50"/>
+    </row>
+    <row r="85" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="73"/>
+      <c r="B85" s="108" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" s="32">
+        <v>1</v>
+      </c>
+      <c r="D85" s="33">
+        <f>2*(PI())*(5/3.281)</f>
+        <v>9.5751071429131152</v>
+      </c>
+      <c r="E85" s="33">
+        <v>1.84</v>
+      </c>
+      <c r="F85" s="33">
+        <f>C85*D85*E85</f>
+        <v>17.618197142960131</v>
+      </c>
+      <c r="G85" s="33">
+        <f>F85</f>
+        <v>17.618197142960131</v>
+      </c>
+      <c r="H85" s="32"/>
+      <c r="I85" s="32"/>
+      <c r="J85" s="32"/>
+      <c r="K85" s="50"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A86" s="73"/>
+      <c r="B86" s="108"/>
+      <c r="C86" s="32">
+        <v>1</v>
+      </c>
+      <c r="D86" s="33">
+        <f>2*(PI())*((5/2)/3.281)</f>
+        <v>4.7875535714565576</v>
+      </c>
+      <c r="E86" s="33">
+        <v>2.84</v>
+      </c>
+      <c r="F86" s="33">
+        <f>C86*D86*E86</f>
+        <v>13.596652142936623</v>
+      </c>
+      <c r="G86" s="33">
+        <f>F86</f>
+        <v>13.596652142936623</v>
+      </c>
+      <c r="H86" s="32"/>
+      <c r="I86" s="32"/>
+      <c r="J86" s="32"/>
+      <c r="K86" s="50"/>
+    </row>
+    <row r="87" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="8"/>
+      <c r="B87" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" s="70"/>
+      <c r="D87" s="65"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="67">
+        <f>SUM(G83:G85)</f>
+        <v>130.40417936840464</v>
+      </c>
+      <c r="H87" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="I87" s="67">
+        <f>3456.96/18.94</f>
+        <v>182.52164730728614</v>
+      </c>
+      <c r="J87" s="72">
+        <f>G87*I87</f>
+        <v>23801.585634076033</v>
+      </c>
+      <c r="K87" s="12"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A88" s="49"/>
+      <c r="B88" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+      <c r="I88" s="32"/>
+      <c r="J88" s="72">
+        <f>0.13*G87*1871.42/18.94</f>
+        <v>1675.0437495232618</v>
+      </c>
+      <c r="K88" s="50"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A89" s="49"/>
+      <c r="B89" s="50"/>
+      <c r="C89" s="50"/>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
+      <c r="H89" s="50"/>
+      <c r="I89" s="50"/>
+      <c r="J89" s="50"/>
+      <c r="K89" s="50"/>
+    </row>
+    <row r="90" spans="1:16" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="49">
+        <v>6</v>
+      </c>
+      <c r="B90" s="109" t="s">
+        <v>74</v>
+      </c>
+      <c r="C90" s="50"/>
+      <c r="D90" s="50"/>
+      <c r="E90" s="50"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50"/>
+      <c r="H90" s="50"/>
+      <c r="I90" s="50"/>
+      <c r="J90" s="50"/>
+      <c r="K90" s="50"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A91" s="73"/>
+      <c r="B91" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C91" s="32">
+        <v>1</v>
+      </c>
+      <c r="D91" s="33">
+        <f>7/3.281</f>
+        <v>2.1334958854007922</v>
+      </c>
+      <c r="E91" s="33">
+        <f>2/3.281</f>
+        <v>0.6095702529716549</v>
+      </c>
+      <c r="F91" s="33"/>
+      <c r="G91" s="33">
+        <f>PI()*D91*SQRT(D91^2+E91^2)</f>
+        <v>14.872137318326605</v>
+      </c>
+      <c r="H91" s="32"/>
+      <c r="I91" s="32"/>
+      <c r="J91" s="32"/>
+      <c r="K91" s="50"/>
+      <c r="M91" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N91" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O91" s="33"/>
+      <c r="P91" s="33">
+        <f>PI()*M91*SQRT(M91^2+N91^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="8"/>
+      <c r="B92" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="70"/>
+      <c r="D92" s="65"/>
+      <c r="E92" s="68"/>
+      <c r="F92" s="68"/>
+      <c r="G92" s="67">
+        <f>SUM(G91:G91)</f>
+        <v>14.872137318326605</v>
+      </c>
+      <c r="H92" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="I92" s="67">
+        <v>1074.98</v>
+      </c>
+      <c r="J92" s="72">
+        <f>G92*I92</f>
+        <v>15987.250174454733</v>
+      </c>
+      <c r="K92" s="12"/>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A93" s="49"/>
+      <c r="B93" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93" s="32"/>
+      <c r="D93" s="32"/>
+      <c r="E93" s="32"/>
+      <c r="F93" s="32"/>
+      <c r="G93" s="32"/>
+      <c r="H93" s="32"/>
+      <c r="I93" s="32"/>
+      <c r="J93" s="72">
+        <f>0.13*G92*(8211.62)/10</f>
+        <v>1587.6164231969228</v>
+      </c>
+      <c r="K93" s="50"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A94" s="49"/>
+      <c r="B94" s="50"/>
+      <c r="C94" s="50"/>
+      <c r="D94" s="50"/>
+      <c r="E94" s="50"/>
+      <c r="F94" s="50"/>
+      <c r="G94" s="50"/>
+      <c r="H94" s="50"/>
+      <c r="I94" s="50"/>
+      <c r="J94" s="50"/>
+      <c r="K94" s="50"/>
+    </row>
+    <row r="95" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="49">
+        <v>7</v>
+      </c>
+      <c r="B95" s="104" t="s">
+        <v>80</v>
+      </c>
+      <c r="C95" s="10">
+        <v>1</v>
+      </c>
+      <c r="D95" s="11"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="14">
+        <f t="shared" ref="G95" si="7">PRODUCT(C95:F95)</f>
+        <v>1</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I95" s="13">
+        <v>20000</v>
+      </c>
+      <c r="J95" s="14">
+        <f>G95*I95</f>
+        <v>20000</v>
+      </c>
+      <c r="K95" s="50"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A96" s="49"/>
+      <c r="B96" s="50"/>
+      <c r="C96" s="50"/>
+      <c r="D96" s="50"/>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
+      <c r="H96" s="50"/>
+      <c r="I96" s="50"/>
+      <c r="J96" s="50"/>
+      <c r="K96" s="50"/>
+    </row>
+    <row r="97" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="8">
+        <v>8</v>
+      </c>
+      <c r="B97" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C82" s="10">
-        <v>1</v>
-      </c>
-      <c r="D82" s="11"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="14">
-        <f t="shared" ref="G82" si="7">PRODUCT(C82:F82)</f>
-        <v>1</v>
-      </c>
-      <c r="H82" s="14" t="s">
+      <c r="C97" s="10">
+        <v>1</v>
+      </c>
+      <c r="D97" s="11"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="14">
+        <f t="shared" ref="G97" si="8">PRODUCT(C97:F97)</f>
+        <v>1</v>
+      </c>
+      <c r="H97" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I82" s="13">
+      <c r="I97" s="13">
         <v>500</v>
       </c>
-      <c r="J82" s="14">
-        <f>G82*I82</f>
+      <c r="J97" s="14">
+        <f>G97*I97</f>
         <v>500</v>
       </c>
-      <c r="K82" s="12"/>
-    </row>
-    <row r="83" spans="1:19" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="8"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="51"/>
-      <c r="K83" s="12"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A84" s="54"/>
-      <c r="B84" s="55" t="s">
+      <c r="K97" s="12"/>
+    </row>
+    <row r="98" spans="1:19" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="8"/>
+      <c r="B98" s="21"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="13"/>
+      <c r="H98" s="14"/>
+      <c r="I98" s="13"/>
+      <c r="J98" s="51"/>
+      <c r="K98" s="12"/>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A99" s="54"/>
+      <c r="B99" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C84" s="56"/>
-      <c r="D84" s="57"/>
-      <c r="E84" s="57"/>
-      <c r="F84" s="57"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="51"/>
-      <c r="I84" s="51"/>
-      <c r="J84" s="51">
-        <f>SUM(J31:J82)</f>
-        <v>665094.84362935787</v>
-      </c>
-      <c r="K84" s="58"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="M85" s="53"/>
-      <c r="N85" s="53"/>
-      <c r="O85" s="53"/>
-      <c r="P85" s="53"/>
-      <c r="Q85" s="53"/>
-      <c r="R85" s="53"/>
-      <c r="S85" s="53"/>
-    </row>
-    <row r="86" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="59"/>
-      <c r="B86" s="60" t="s">
+      <c r="C99" s="56"/>
+      <c r="D99" s="57"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="57"/>
+      <c r="G99" s="51"/>
+      <c r="H99" s="51"/>
+      <c r="I99" s="51"/>
+      <c r="J99" s="51">
+        <f>SUM(J31:J97)</f>
+        <v>728146.33961060888</v>
+      </c>
+      <c r="K99" s="58"/>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="M100" s="53"/>
+      <c r="N100" s="53"/>
+      <c r="O100" s="53"/>
+      <c r="P100" s="53"/>
+      <c r="Q100" s="53"/>
+      <c r="R100" s="53"/>
+      <c r="S100" s="53"/>
+    </row>
+    <row r="101" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="59"/>
+      <c r="B101" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="C86" s="78">
-        <f>J84</f>
-        <v>665094.84362935787</v>
-      </c>
-      <c r="D86" s="79"/>
-      <c r="E86" s="42">
+      <c r="C101" s="97">
+        <f>J99</f>
+        <v>728146.33961060888</v>
+      </c>
+      <c r="D101" s="98"/>
+      <c r="E101" s="42">
         <v>100</v>
       </c>
-      <c r="F86" s="59"/>
-      <c r="G86" s="61"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="62"/>
-      <c r="J86" s="63"/>
-      <c r="K86" s="64"/>
-      <c r="M86" s="52"/>
-      <c r="N86" s="52"/>
-      <c r="O86" s="52"/>
-      <c r="P86" s="52"/>
-      <c r="Q86" s="52"/>
-      <c r="R86" s="52"/>
-      <c r="S86" s="52"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B87" s="60" t="s">
+      <c r="F101" s="59"/>
+      <c r="G101" s="61"/>
+      <c r="H101" s="59"/>
+      <c r="I101" s="62"/>
+      <c r="J101" s="63"/>
+      <c r="K101" s="64"/>
+      <c r="M101" s="52"/>
+      <c r="N101" s="52"/>
+      <c r="O101" s="52"/>
+      <c r="P101" s="52"/>
+      <c r="Q101" s="52"/>
+      <c r="R101" s="52"/>
+      <c r="S101" s="52"/>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B102" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C87" s="82">
-        <v>500000</v>
-      </c>
-      <c r="D87" s="83"/>
-      <c r="E87" s="42"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="60" t="s">
+      <c r="C102" s="101">
+        <v>650000</v>
+      </c>
+      <c r="D102" s="102"/>
+      <c r="E102" s="42"/>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B103" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C88" s="82">
-        <f>C87-C90-C91</f>
-        <v>475000</v>
-      </c>
-      <c r="D88" s="83"/>
-      <c r="E88" s="42">
-        <f>C88/C86*100</f>
-        <v>71.418385595649966</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B89" s="60" t="s">
+      <c r="C103" s="101">
+        <f>C102-C105-C106</f>
+        <v>617500</v>
+      </c>
+      <c r="D103" s="102"/>
+      <c r="E103" s="42">
+        <f>C103/C101*100</f>
+        <v>84.804381538224959</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B104" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="C89" s="84">
-        <f>C86-C88</f>
-        <v>190094.84362935787</v>
-      </c>
-      <c r="D89" s="84"/>
-      <c r="E89" s="42">
-        <f>100-E88</f>
-        <v>28.581614404350034</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B90" s="60" t="s">
+      <c r="C104" s="103">
+        <f>C101-C103</f>
+        <v>110646.33961060888</v>
+      </c>
+      <c r="D104" s="103"/>
+      <c r="E104" s="42">
+        <f>100-E103</f>
+        <v>15.195618461775041</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B105" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="C90" s="78">
-        <f>C87*0.03</f>
-        <v>15000</v>
-      </c>
-      <c r="D90" s="79"/>
-      <c r="E90" s="42">
+      <c r="C105" s="97">
+        <f>C102*0.03</f>
+        <v>19500</v>
+      </c>
+      <c r="D105" s="98"/>
+      <c r="E105" s="42">
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B91" s="60" t="s">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B106" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C91" s="78">
-        <f>C87*0.02</f>
-        <v>10000</v>
-      </c>
-      <c r="D91" s="79"/>
-      <c r="E91" s="42">
+      <c r="C106" s="97">
+        <f>C102*0.02</f>
+        <v>13000</v>
+      </c>
+      <c r="D106" s="98"/>
+      <c r="E106" s="42">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -5792,19 +6242,12 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>